--- a/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,57</t>
+          <t>0,38; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,57</t>
+          <t>0,44; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,2</t>
+          <t>0,67; 3,28</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,21</t>
+          <t>0,42; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,47</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,32</t>
+          <t>0,94; 3,39</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,15</t>
+          <t>0,26; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,39</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,75</t>
+          <t>0,73; 4,0</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,91</t>
+          <t>0,65; 3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,08</t>
+          <t>1,66; 6,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,81</t>
+          <t>1,46; 4,51</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,33</t>
+          <t>0,85; 2,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,74</t>
+          <t>1,61; 3,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,79</t>
+          <t>1,4; 2,68</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>439; 5140</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>605; 6595</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1704; 8277</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2674</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5526</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>776; 6085</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2472; 11448</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4126; 14871</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6096</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>485; 5232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1311; 12391</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2690; 14702</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9501</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1045; 6272</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2939; 12097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4953; 15238</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5561; 15312</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11953; 27301</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19501; 37362</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,42</t>
+          <t>0,38; 4,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,84</t>
+          <t>0,44; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,28</t>
+          <t>0,68; 3,35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,26</t>
+          <t>0,42; 3,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>1,0; 4,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,39</t>
+          <t>1,05; 3,38</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,78</t>
+          <t>0,27; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,91</t>
+          <t>0,71; 6,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,0</t>
+          <t>0,65; 3,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,9</t>
+          <t>0,65; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,83</t>
+          <t>1,83; 7,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,51</t>
+          <t>1,56; 4,97</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,35</t>
+          <t>0,84; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,67</t>
+          <t>1,54; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,68</t>
+          <t>1,42; 2,72</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>439; 5140</t>
+          <t>438; 5164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>605; 6595</t>
+          <t>593; 7117</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1704; 8277</t>
+          <t>1715; 8452</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>776; 6085</t>
+          <t>784; 6431</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2472; 11448</t>
+          <t>2519; 11470</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4126; 14871</t>
+          <t>4599; 14826</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>485; 5232</t>
+          <t>507; 5785</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1311; 12391</t>
+          <t>1279; 11019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2690; 14702</t>
+          <t>2403; 13776</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1045; 6272</t>
+          <t>1039; 6499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2939; 12097</t>
+          <t>3249; 14070</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4953; 15238</t>
+          <t>5279; 16820</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5561; 15312</t>
+          <t>5503; 14974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11953; 27301</t>
+          <t>11441; 27479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19501; 37362</t>
+          <t>19836; 37938</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,44</t>
+          <t>0,5; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,22</t>
+          <t>0,3; 4,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,35</t>
+          <t>0,63; 3,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,44</t>
+          <t>0,82; 4,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,57</t>
+          <t>0,49; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,38</t>
+          <t>0,98; 3,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,08</t>
+          <t>0,66; 5,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,15</t>
+          <t>0,24; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,75</t>
+          <t>0,76; 3,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,04</t>
+          <t>1,87; 7,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,94</t>
+          <t>0,61; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,97</t>
+          <t>1,55; 4,9</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,69</t>
+          <t>0,87; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,72</t>
+          <t>1,48; 2,84</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>4028</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>438; 5164</t>
+          <t>612; 6433</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>593; 7117</t>
+          <t>356; 5413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1715; 8452</t>
+          <t>1516; 8652</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7882</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>784; 6431</t>
+          <t>1913; 10565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2519; 11470</t>
+          <t>885; 6642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4599; 14826</t>
+          <t>4058; 14026</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5214</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>507; 5785</t>
+          <t>1063; 9414</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1279; 11019</t>
+          <t>377; 5547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2403; 13776</t>
+          <t>2393; 11717</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9238</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1039; 6499</t>
+          <t>3102; 12352</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3249; 14070</t>
+          <t>986; 5899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5279; 16820</t>
+          <t>5069; 16008</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26362</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5503; 14974</t>
+          <t>10614; 25844</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11441; 27479</t>
+          <t>5391; 15045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19836; 37938</t>
+          <t>19253; 36980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 5,28</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 4,5</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 3,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 4,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 3,67</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 3,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 5,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 3,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 3,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 7,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,61; 3,66</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 4,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 3,78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 2,44</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.01834274788970192</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.01490807121543672</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01663598192966998</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1794</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.005026826769026186</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.00296006145619649</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.006262070474360998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>612; 6433</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>356; 5413</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1516; 8652</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.05280882066262056</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.04498795406703362</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.03573153676570697</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02197809933884027</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01520180780894038</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01902036163775586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2750</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7882</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.008193246274881822</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.00489354707786055</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.009792984889270653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1913; 10565</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>885; 6642</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4058; 14026</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04524428011645793</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03672309145162675</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03384725829725024</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02029772863277199</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01246656385733894</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01647013497963336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3285</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1929</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5214</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.00656843337507432</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.002436353215523334</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.007559814082441831</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1063; 9414</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>377; 5547</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2393; 11717</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05816634094461987</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.03584805880375006</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.0370109616369802</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.03941747439848543</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01675554286103628</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.02825763925134432</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6540</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2697</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9238</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01869647533405913</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.006122622412573261</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01550582711901576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>3102; 12352</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>986; 5899</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5069; 16008</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.0744444947892032</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.03664185671569545</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.04896608650360306</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.02516791528644101</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01486395680080411</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.02027821920810732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>17192</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9170</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>26362</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.01553903643119006</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.008737983143996084</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01481036645547883</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>10614; 25844</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5391; 15045</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19253; 36980</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.03783487268015984</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02438814627909491</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02844623123686095</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2234</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1794</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>612</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>356</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6433</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5413</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8652</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5132</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>885</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>10565</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>6642</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>14026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3285</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5214</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>377</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>5547</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>11717</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>6540</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>2697</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>9238</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3102</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>986</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5069</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>12352</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>5899</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>16008</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>17192</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9170</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>26362</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>10614</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>5391</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>19253</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>25844</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>15045</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>36980</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>